--- a/examples/sample_audit.xlsx
+++ b/examples/sample_audit.xlsx
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary'!$A$1:$T$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$F$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CIS Checks'!$A$1:$E$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Disk'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Listening Ports'!$A$1:$D$6</definedName>
@@ -565,7 +565,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09 12:05:49</t>
+          <t>2026-07-17 18:52:48</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09.formula-safe</t>
+          <t>2026-07-17.plan-export</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1573,9 +1573,9 @@
           <t>Firewall</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>active</t>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>INACTIVE</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>15 / 10 / 4</t>
+          <t>14 / 11 / 4</t>
         </is>
       </c>
     </row>
@@ -1744,36 +1744,36 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>[Patching] 7 pending security update(s) — Apply security updates promptly</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>[Firewall] No active host firewall detected — Enable ufw/firewalld/nftables with a default-deny inbound policy</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>[Patching] Reboot required — Schedule a maintenance reboot</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>[Patching] 7 pending security update(s) — Apply security updates promptly</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>[Accounts] Multiple UID 0 accounts — Only 'root' should have UID 0; investigate the others</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>[Patching] Reboot required — Schedule a maintenance reboot</t>
         </is>
       </c>
     </row>
@@ -1784,6 +1784,18 @@
         </is>
       </c>
       <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>[Accounts] Multiple UID 0 accounts — Only 'root' should have UID 0; investigate the others</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>[Accounts] Login account(s) with empty password — Lock or set passwords on these accounts</t>
         </is>
@@ -2360,9 +2372,9 @@
       <c r="J2" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>INACTIVE</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -2398,12 +2410,12 @@
       </c>
       <c r="S2" s="6" t="inlineStr">
         <is>
-          <t>10/4</t>
+          <t>11/4</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
         <is>
-          <t>5/2/3</t>
+          <t>5/3/3</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2825,22 +2837,22 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Patching</t>
+          <t>Firewall</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Reboot required</t>
+          <t>No active host firewall detected</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>kernel/libs updated</t>
+          <t>ufw:Status: inactive; iptables_rules:2</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Schedule a maintenance reboot</t>
+          <t>Enable ufw/firewalld/nftables with a default-deny inbound policy</t>
         </is>
       </c>
     </row>
@@ -2850,29 +2862,29 @@
           <t>web01.example.com</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>SSH</t>
+          <t>Patching</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>X11 forwarding enabled</t>
+          <t>Reboot required</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>x11forwarding yes</t>
+          <t>kernel/libs updated</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Disable unless required</t>
+          <t>Schedule a maintenance reboot</t>
         </is>
       </c>
     </row>
@@ -2894,17 +2906,17 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>MaxAuthTries is high</t>
+          <t>X11 forwarding enabled</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>x11forwarding yes</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Lower to 3-4 to slow brute forcing</t>
+          <t>Disable unless required</t>
         </is>
       </c>
     </row>
@@ -2921,27 +2933,59 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
+          <t>SSH</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>MaxAuthTries is high</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Lower to 3-4 to slow brute forcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>web01.example.com</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
           <t>Patching</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>No automatic security updates configured</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>auto-updates:none-detected</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Consider unattended-upgrades / dnf-automatic for security patches</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F13"/>
+  <autoFilter ref="A1:F14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3834,12 +3878,12 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>5.2.1</t>
+          <t>3.5.1</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>SSH: root login disabled</t>
+          <t>Host firewall active</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -3849,7 +3893,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>PermitRootLogin=yes</t>
+          <t>ufw:Status: inactive; iptables_rules:2</t>
         </is>
       </c>
     </row>
@@ -3861,12 +3905,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>5.2.4</t>
+          <t>5.2.1</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>SSH: MaxAuthTries &lt;= 4</t>
+          <t>SSH: root login disabled</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
@@ -3876,7 +3920,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>MaxAuthTries=6</t>
+          <t>PermitRootLogin=yes</t>
         </is>
       </c>
     </row>
@@ -3888,12 +3932,12 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>5.2.6</t>
+          <t>5.2.4</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>SSH: idle timeout configured (ClientAliveInterval 1-300)</t>
+          <t>SSH: MaxAuthTries &lt;= 4</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -3903,7 +3947,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>ClientAliveInterval=0</t>
+          <t>MaxAuthTries=6</t>
         </is>
       </c>
     </row>
@@ -3915,12 +3959,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>5.2.7</t>
+          <t>5.2.6</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>SSH: LoginGraceTime &lt;= 60</t>
+          <t>SSH: idle timeout configured (ClientAliveInterval 1-300)</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
@@ -3930,7 +3974,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>LoginGraceTime=120</t>
+          <t>ClientAliveInterval=0</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3986,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>5.2.7</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>PASS_MAX_DAYS &lt;= 365</t>
+          <t>SSH: LoginGraceTime &lt;= 60</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -3957,7 +4001,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>PASS_MAX_DAYS=99999</t>
+          <t>LoginGraceTime=120</t>
         </is>
       </c>
     </row>
@@ -3969,12 +4013,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>5.4.1</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>PASS_MIN_DAYS &gt;= 1</t>
+          <t>PASS_MAX_DAYS &lt;= 365</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -3984,7 +4028,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>PASS_MIN_DAYS=0</t>
+          <t>PASS_MAX_DAYS=99999</t>
         </is>
       </c>
     </row>
@@ -3996,12 +4040,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>6.2.1</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Only one UID 0 account (root)</t>
+          <t>PASS_MIN_DAYS &gt;= 1</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -4011,7 +4055,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>backup2, root</t>
+          <t>PASS_MIN_DAYS=0</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4067,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>6.2.2</t>
+          <t>6.2.1</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>No login accounts with empty password</t>
+          <t>Only one UID 0 account (root)</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
@@ -4038,7 +4082,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>backup2, root</t>
         </is>
       </c>
     </row>
@@ -4050,22 +4094,22 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>6.2.2</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>No reboot pending</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>WARN</t>
+          <t>No login accounts with empty password</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>test</t>
         </is>
       </c>
     </row>
@@ -4077,12 +4121,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Automatic security updates configured</t>
+          <t>No reboot pending</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -4092,7 +4136,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>auto-updates:none-detected</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -4104,12 +4148,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>5.2.2</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>SSH: password authentication disabled</t>
+          <t>Automatic security updates configured</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -4119,7 +4163,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>PasswordAuthentication=yes</t>
+          <t>auto-updates:none-detected</t>
         </is>
       </c>
     </row>
@@ -4131,12 +4175,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>5.2.5</t>
+          <t>5.2.2</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>SSH: X11 forwarding disabled</t>
+          <t>SSH: password authentication disabled</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -4146,7 +4190,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>X11Forwarding=yes</t>
+          <t>PasswordAuthentication=yes</t>
         </is>
       </c>
     </row>
@@ -4158,22 +4202,22 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>5.2.5</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>ASLR enabled (randomize_va_space=2)</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>SSH: X11 forwarding disabled</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>randomize_va_space=2</t>
+          <t>X11Forwarding=yes</t>
         </is>
       </c>
     </row>
@@ -4185,12 +4229,12 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>1.6.1</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Mandatory Access Control active (SELinux/AppArmor)</t>
+          <t>ASLR enabled (randomize_va_space=2)</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
@@ -4200,7 +4244,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>selinux=absent apparmor=enabled</t>
+          <t>randomize_va_space=2</t>
         </is>
       </c>
     </row>
@@ -4212,12 +4256,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>1.6.1</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Time synchronization in use</t>
+          <t>Mandatory Access Control active (SELinux/AppArmor)</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -4227,7 +4271,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>NTP=yes synced=yes</t>
+          <t>selinux=absent apparmor=enabled</t>
         </is>
       </c>
     </row>
@@ -4239,12 +4283,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>3.2.1</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>IP forwarding disabled</t>
+          <t>Time synchronization in use</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
@@ -4254,7 +4298,7 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>ip_forward=0 (WARN=router/gateway ok)</t>
+          <t>NTP=yes synced=yes</t>
         </is>
       </c>
     </row>
@@ -4266,12 +4310,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>3.2.2</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>ICMP redirects not accepted</t>
+          <t>IP forwarding disabled</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -4281,7 +4325,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>accept_redirects=0</t>
+          <t>ip_forward=0 (WARN=router/gateway ok)</t>
         </is>
       </c>
     </row>
@@ -4293,12 +4337,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>3.2.3</t>
+          <t>3.2.2</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>TCP SYN cookies enabled</t>
+          <t>ICMP redirects not accepted</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -4308,7 +4352,7 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>tcp_syncookies=1</t>
+          <t>accept_redirects=0</t>
         </is>
       </c>
     </row>
@@ -4320,12 +4364,12 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>3.2.4</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Reverse path filtering enabled</t>
+          <t>TCP SYN cookies enabled</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -4335,7 +4379,7 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>rp_filter=1</t>
+          <t>tcp_syncookies=1</t>
         </is>
       </c>
     </row>
@@ -4347,12 +4391,12 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>3.5.1</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Host firewall active</t>
+          <t>Reverse path filtering enabled</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
@@ -4362,7 +4406,7 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>ufw:Status: inactive; iptables_rules:2</t>
+          <t>rp_filter=1</t>
         </is>
       </c>
     </row>
